--- a/results/DR_results/01_pollution_assessment/HZD_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/DR_results/01_pollution_assessment/HZD_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8244804157151132</v>
+        <v>0.8928102114541755</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.05311750570932072</v>
+        <v>0.356861268725053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9394739841417263</v>
+        <v>1.665849375330178</v>
       </c>
       <c r="G2" t="n">
-        <v>0.603</v>
+        <v>0.425</v>
       </c>
       <c r="H2" t="n">
-        <v>133.5571773642743</v>
+        <v>141.7596441484756</v>
       </c>
       <c r="I2" t="n">
-        <v>161.9895085663538</v>
+        <v>158.7791473818191</v>
       </c>
       <c r="J2" t="n">
-        <v>12.3885529463556</v>
+        <v>13.07919000582602</v>
       </c>
       <c r="K2" t="n">
-        <v>7.03391994943152</v>
+        <v>2.571570014352007</v>
       </c>
     </row>
     <row r="3">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="D6" t="n">
-        <v>0.449293478042906</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2198324272274502</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F6" t="n">
-        <v>1.958038091633472</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G6" t="n">
-        <v>0.029</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>193.14707745346</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I6" t="n">
-        <v>429.8906770131551</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J6" t="n">
-        <v>8.393238376284554</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K6" t="n">
-        <v>1.739698173454825</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4479300749834989</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2639067666446653</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F7" t="n">
-        <v>2.434094240707521</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G7" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>228.1510323938571</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I7" t="n">
-        <v>509.3451972437034</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J7" t="n">
-        <v>8.076120227332632</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K7" t="n">
-        <v>1.496397354728379</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4217418588551418</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2611145974260146</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F8" t="n">
-        <v>2.625593284121481</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>257.2491079423793</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I8" t="n">
-        <v>609.9681654571978</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J8" t="n">
-        <v>7.318956066729745</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K8" t="n">
-        <v>1.496264214432533</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4055866662648849</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2640596820422383</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F9" t="n">
-        <v>2.86579035434562</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>268.1360486914178</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I9" t="n">
-        <v>661.1066659580488</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J9" t="n">
-        <v>7.035866954332976</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K9" t="n">
-        <v>1.371921071780211</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>30</v>
+        <v>146</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4062323264813978</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2825307278316891</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F10" t="n">
-        <v>3.28396989946543</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>313.9674073825032</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I10" t="n">
-        <v>772.8764721949825</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J10" t="n">
-        <v>7.656144344634576</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K10" t="n">
-        <v>1.440885776399651</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4205296654963147</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3132203442919285</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F11" t="n">
-        <v>3.918854958511525</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>357.5353620195011</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I11" t="n">
-        <v>850.2024740574084</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J11" t="n">
-        <v>8.402641749750053</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K11" t="n">
-        <v>1.479812261807552</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>36</v>
+        <v>146</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4038834899277807</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3045307382490774</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F12" t="n">
-        <v>4.065146491703611</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>385.547946446415</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I12" t="n">
-        <v>954.6018989668426</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J12" t="n">
-        <v>8.4390876327502</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K12" t="n">
-        <v>1.440249014722778</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>146</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3817174026733341</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2880382212602028</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F13" t="n">
-        <v>4.074730339390305</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>381.5288171667727</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I13" t="n">
-        <v>999.5059551772051</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J13" t="n">
-        <v>7.681922581572643</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K13" t="n">
-        <v>1.590799346697633</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3713024264649473</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2839833190295233</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F14" t="n">
-        <v>4.252247158384441</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>389.5017811554005</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I14" t="n">
-        <v>1049.014909123335</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J14" t="n">
-        <v>7.035176596448729</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K14" t="n">
-        <v>1.568885642892785</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>146</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3645297531784105</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2830592087141041</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F15" t="n">
-        <v>4.474374825592545</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>409.7799985347065</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I15" t="n">
-        <v>1124.13320164335</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J15" t="n">
-        <v>7.160348707117757</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K15" t="n">
-        <v>1.648791734038844</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>146</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3323974677960599</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2529209758670194</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F16" t="n">
-        <v>4.182336936723831</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>403.0031769064273</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I16" t="n">
-        <v>1212.413498750499</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J16" t="n">
-        <v>6.677412284820579</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K16" t="n">
-        <v>1.604632378104638</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3435497596278718</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2706108440309687</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F17" t="n">
-        <v>4.710102375616594</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>452.8863701153541</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I17" t="n">
-        <v>1318.255528997937</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J17" t="n">
-        <v>7.203086869661853</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K17" t="n">
-        <v>1.652413151252307</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>146</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3320532701384984</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E18" t="n">
-        <v>0.2624754857779252</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F18" t="n">
-        <v>4.772403622651992</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>470.4102489449058</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I18" t="n">
-        <v>1416.671032177154</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J18" t="n">
-        <v>6.981439630771719</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K18" t="n">
-        <v>1.589801370266566</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3257304420184426</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2583034862202868</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F19" t="n">
-        <v>4.830863831277283</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>471.7155814228368</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I19" t="n">
-        <v>1448.177758577838</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J19" t="n">
-        <v>6.584551996337243</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K19" t="n">
-        <v>1.556478708838896</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>146</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3094191268955122</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2442699879233907</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F20" t="n">
-        <v>4.749397026228055</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>469.6271254529725</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I20" t="n">
-        <v>1517.770184942578</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J20" t="n">
-        <v>6.307887184043505</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K20" t="n">
-        <v>1.554790737440042</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3105206052533805</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2489599450081466</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F21" t="n">
-        <v>5.044140267768185</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>503.2973623085833</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I21" t="n">
-        <v>1620.817922526912</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J21" t="n">
-        <v>6.421094329085269</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K21" t="n">
-        <v>1.540704099913061</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>65</v>
+        <v>146</v>
       </c>
       <c r="D22" t="n">
-        <v>0.3086799156935251</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2500934678709426</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F22" t="n">
-        <v>5.268793845093678</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>538.2285966694741</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I22" t="n">
-        <v>1743.646312265609</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J22" t="n">
-        <v>6.694654480153982</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K22" t="n">
-        <v>1.476840707745239</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3168374036269357</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2617436458549144</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F23" t="n">
-        <v>5.750876622684062</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>575.4156650222669</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I23" t="n">
-        <v>1816.122902268817</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J23" t="n">
-        <v>6.9077380897434</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K23" t="n">
-        <v>1.478299119575941</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>71</v>
+        <v>146</v>
       </c>
       <c r="D24" t="n">
-        <v>0.312275825879006</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2593739663312372</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F24" t="n">
-        <v>5.902927204232402</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>591.0181826142995</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I24" t="n">
-        <v>1892.615865959777</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J24" t="n">
-        <v>6.77659799194184</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K24" t="n">
-        <v>1.484757632116551</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1293,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3103998804941434</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E25" t="n">
-        <v>0.2596939893540069</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F25" t="n">
-        <v>6.121574308521416</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>638.8186853065999</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I25" t="n">
-        <v>2058.050680591848</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J25" t="n">
-        <v>7.198337712267131</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K25" t="n">
-        <v>1.480469801129502</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1328,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="D26" t="n">
-        <v>0.3026607637304653</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2535523668100755</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F26" t="n">
-        <v>6.163116344870971</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>641.3400417002642</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I26" t="n">
-        <v>2119.006222661256</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J26" t="n">
-        <v>7.061609412326357</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K26" t="n">
-        <v>1.525605288713949</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1363,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2908174926230815</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2428997556381547</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F27" t="n">
-        <v>6.069099062724131</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>637.2202286788514</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I27" t="n">
-        <v>2191.134456635766</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J27" t="n">
-        <v>6.843105976699015</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K27" t="n">
-        <v>1.483341338141053</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1398,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2938176785092581</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2479616836072619</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F28" t="n">
-        <v>6.407399493505864</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>668.2524985600758</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I28" t="n">
-        <v>2274.378117581578</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J28" t="n">
-        <v>6.999805874951482</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K28" t="n">
-        <v>1.468576057575147</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1433,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>86</v>
+        <v>146</v>
       </c>
       <c r="D29" t="n">
-        <v>0.292982887472903</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2487943179399594</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F29" t="n">
-        <v>6.630286758988153</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>687.9413376151863</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I29" t="n">
-        <v>2348.059791303721</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J29" t="n">
-        <v>7.008481527442683</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K29" t="n">
-        <v>1.457480110908639</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1468,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2968561751217216</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2544981133820662</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F30" t="n">
-        <v>7.008256821246541</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>708.5905462613341</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I30" t="n">
-        <v>2386.982672571277</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J30" t="n">
-        <v>7.020713959809245</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K30" t="n">
-        <v>1.465510654369599</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1503,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2977821649646551</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2564752334919878</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F31" t="n">
-        <v>7.20901200714211</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>723.5860698607678</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I31" t="n">
-        <v>2429.917419489017</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J31" t="n">
-        <v>6.976664005584686</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K31" t="n">
-        <v>1.446146009710105</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1538,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>94</v>
+        <v>146</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2862725519954962</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2457198560861494</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F32" t="n">
-        <v>7.059273016902298</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>731.7211136579933</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I32" t="n">
-        <v>2556.029589834743</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J32" t="n">
-        <v>6.907997361506187</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K32" t="n">
-        <v>1.497620194219961</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1573,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2772448868223252</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2375330674169585</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F33" t="n">
-        <v>6.981419914113975</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>734.4268144989859</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I33" t="n">
-        <v>2649.018428857985</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J33" t="n">
-        <v>6.678511102502083</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K33" t="n">
-        <v>1.508809585769558</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1608,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>146</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2767923403307312</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E34" t="n">
-        <v>0.2383238477951318</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F34" t="n">
-        <v>7.195299895741501</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>749.757356743728</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I34" t="n">
-        <v>2708.735927619473</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J34" t="n">
-        <v>6.640447285113613</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K34" t="n">
-        <v>1.524693224095755</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1643,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="D35" t="n">
-        <v>0.275050149914202</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E35" t="n">
-        <v>0.2376816009407072</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F35" t="n">
-        <v>7.360471772915059</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>765.4792103553575</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I35" t="n">
-        <v>2783.053238088174</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J35" t="n">
-        <v>6.587768098208617</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K35" t="n">
-        <v>1.501234803968533</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1678,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2690090572658769</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2324595101291707</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F36" t="n">
-        <v>7.36012012022209</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>783.3191776047468</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I36" t="n">
-        <v>2911.869159968648</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J36" t="n">
-        <v>6.634441701312149</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K36" t="n">
-        <v>1.449241607191143</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1713,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2770706171390691</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E37" t="n">
-        <v>0.241976957776888</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F37" t="n">
-        <v>7.895175999732177</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>828.3348221221386</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I37" t="n">
-        <v>2989.616259837381</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J37" t="n">
-        <v>6.847491535728425</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K37" t="n">
-        <v>1.413825333818857</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1748,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2772913295923938</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2432012979693934</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F38" t="n">
-        <v>8.13408836515444</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>857.9887661555828</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I38" t="n">
-        <v>3094.178124562311</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J38" t="n">
-        <v>6.931404051945393</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K38" t="n">
-        <v>1.400136376747712</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1783,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2717962284868438</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E39" t="n">
-        <v>0.2383923857568826</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F39" t="n">
-        <v>8.136675492219899</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>862.8890901884274</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I39" t="n">
-        <v>3174.764767680341</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J39" t="n">
-        <v>6.731095903406381</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K39" t="n">
-        <v>1.40291760863367</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1818,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2682540455330982</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2355868154229686</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F40" t="n">
-        <v>8.211716898823239</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>877.3981186992747</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I40" t="n">
-        <v>3270.773109705136</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J40" t="n">
-        <v>6.613282546138826</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K40" t="n">
-        <v>1.396563563842213</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1853,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2795684643948632</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2482453541511617</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F41" t="n">
-        <v>8.925309850131454</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>941.2429862753628</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I41" t="n">
-        <v>3366.770956490818</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J41" t="n">
-        <v>7.004265835884761</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K41" t="n">
-        <v>1.367986952368172</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1888,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2802107398851459</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E42" t="n">
-        <v>0.2497111949650249</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F42" t="n">
-        <v>9.18737445489842</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>967.3428039959271</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I42" t="n">
-        <v>3452.197458214579</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J42" t="n">
-        <v>6.994264555735413</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K42" t="n">
-        <v>1.355109366833076</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1923,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2779562779460951</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E43" t="n">
-        <v>0.2481197605058511</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F43" t="n">
-        <v>9.315975917859063</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>977.3411520312011</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I43" t="n">
-        <v>3516.168655203894</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J43" t="n">
-        <v>6.850710195247925</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K43" t="n">
-        <v>1.365289764091508</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1958,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2882383072256346</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2593049050803351</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F44" t="n">
-        <v>9.96212978266928</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1039.814171685818</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I44" t="n">
-        <v>3607.48084352246</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J44" t="n">
-        <v>7.252545373879746</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K44" t="n">
-        <v>1.323577116192946</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1993,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2874429201132372</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E45" t="n">
-        <v>0.259166845514556</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F45" t="n">
-        <v>10.16558784035195</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1066.325132014533</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I45" t="n">
-        <v>3709.69349878041</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J45" t="n">
-        <v>7.326982379380316</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K45" t="n">
-        <v>1.330041916169805</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +2028,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D46" t="n">
-        <v>0.285347945894472</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E46" t="n">
-        <v>0.2576482538748778</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F46" t="n">
-        <v>10.30148442418145</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1085.41357860823</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I46" t="n">
-        <v>3803.824748784559</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J46" t="n">
-        <v>7.229809383641905</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K46" t="n">
-        <v>1.347140068109186</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2063,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2815114238844844</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2542959475164726</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F47" t="n">
-        <v>10.34379924414486</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1097.566679727549</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I47" t="n">
-        <v>3898.835310420389</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J47" t="n">
-        <v>7.115806263965744</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K47" t="n">
-        <v>1.339466824365082</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2098,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2783302082392444</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2516016974332906</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F48" t="n">
-        <v>10.41323290548777</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1108.836094668159</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I48" t="n">
-        <v>3983.886986909578</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J48" t="n">
-        <v>6.980612693000444</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K48" t="n">
-        <v>1.343530135594489</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2544314571811545</v>
+        <v>0.2603250325493759</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2274181041804717</v>
+        <v>0.2339080694261393</v>
       </c>
       <c r="F49" t="n">
-        <v>9.418729217906533</v>
+        <v>9.854464774582363</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1032.997141897663</v>
+        <v>1077.864258170404</v>
       </c>
       <c r="I49" t="n">
-        <v>4060.02132496601</v>
+        <v>4140.455674257779</v>
       </c>
       <c r="J49" t="n">
-        <v>6.365241565698738</v>
+        <v>6.602794217144437</v>
       </c>
       <c r="K49" t="n">
-        <v>1.333067444284535</v>
+        <v>1.335006172696414</v>
       </c>
     </row>
   </sheetData>
